--- a/model_outputs_paper1/TASK_A_SCIM/metrics_SCIM_3class.xlsx
+++ b/model_outputs_paper1/TASK_A_SCIM/metrics_SCIM_3class.xlsx
@@ -485,40 +485,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7939393939393939</v>
+        <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7795031055900621</v>
+        <v>0.7845222410439802</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7892117253904405</v>
+        <v>0.7956923734701512</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
         <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -528,19 +528,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7818181818181819</v>
+        <v>0.7757575757575758</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7569483656440178</v>
+        <v>0.7620616098876969</v>
       </c>
       <c r="C3" t="n">
-        <v>0.76838836100122</v>
+        <v>0.7688788050671205</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -549,152 +549,152 @@
         <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7696969696969697</v>
+        <v>0.7757575757575758</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7592697157914549</v>
+        <v>0.7526193613150135</v>
       </c>
       <c r="C4" t="n">
-        <v>0.765724840660902</v>
+        <v>0.761488779419814</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7515151515151515</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6948365644017818</v>
+        <v>0.746282702804442</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7142317538653105</v>
+        <v>0.7522148394241417</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>HistGB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7212121212121212</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7319154275676015</v>
+        <v>0.6789635485287659</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7352609738282107</v>
+        <v>0.7003169509320338</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>HistGB</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
     </row>
